--- a/Fase 1/Gantt Capstone.xlsx
+++ b/Fase 1/Gantt Capstone.xlsx
@@ -82,16 +82,16 @@
     <t>FASE 2 (Desarrollo)</t>
   </si>
   <si>
-    <t>Desarrollo</t>
-  </si>
-  <si>
-    <t>Actividad 2.2</t>
-  </si>
-  <si>
-    <t>Actividad 2.3</t>
-  </si>
-  <si>
-    <t>Actividad 2.4</t>
+    <t>Reglas de negocio</t>
+  </si>
+  <si>
+    <t>Backend</t>
+  </si>
+  <si>
+    <t>Arquitectura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrollo </t>
   </si>
   <si>
     <t>Actividad 2.5</t>
